--- a/data/trans_bre/IP04D$aparatos-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Clase-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 13,79</t>
+          <t>-8,62; 15,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 11,22</t>
+          <t>-12,39; 10,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 17,45</t>
+          <t>-5,86; 17,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 34,64</t>
+          <t>-16,66; 38,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 29,09</t>
+          <t>-25,27; 28,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 47,68</t>
+          <t>-11,8; 48,22</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 21,15</t>
+          <t>-4,82; 19,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 19,02</t>
+          <t>-2,79; 20,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 12,42</t>
+          <t>-11,67; 13,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 51,23</t>
+          <t>-8,72; 46,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 52,38</t>
+          <t>-5,75; 54,83</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 24,01</t>
+          <t>-19,03; 27,39</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 11,71</t>
+          <t>-12,57; 11,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 19,55</t>
+          <t>-9,45; 17,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 12,21</t>
+          <t>-16,9; 13,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,97; 20,23</t>
+          <t>-17,69; 18,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 45,76</t>
+          <t>-16,52; 41,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 20,7</t>
+          <t>-23,67; 24,55</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 14,64</t>
+          <t>-0,41; 14,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 1,65</t>
+          <t>-14,21; 1,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,98; 18,65</t>
+          <t>-7,39; 18,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 25,07</t>
+          <t>-0,6; 25,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 3,37</t>
+          <t>-23,41; 3,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 33,37</t>
+          <t>-11,63; 31,87</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 8,3</t>
+          <t>-9,04; 9,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 12,25</t>
+          <t>-6,79; 11,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 19,53</t>
+          <t>-6,12; 19,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,06; 13,01</t>
+          <t>-12,88; 15,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 21,91</t>
+          <t>-10,18; 21,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 35,21</t>
+          <t>-8,68; 37,43</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 14,38</t>
+          <t>-13,03; 13,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 9,96</t>
+          <t>-20,79; 8,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 13,52</t>
+          <t>-13,19; 13,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 21,05</t>
+          <t>-16,59; 19,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 19,52</t>
+          <t>-32,59; 17,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 22,15</t>
+          <t>-17,48; 22,48</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 7,43</t>
+          <t>-0,97; 8,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 4,68</t>
+          <t>-4,54; 4,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 9,6</t>
+          <t>-2,18; 9,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 12,62</t>
+          <t>-1,62; 13,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 9,26</t>
+          <t>-8,39; 8,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 16,96</t>
+          <t>-3,58; 16,44</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Clase-trans_bre.xlsx
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 15,06</t>
+          <t>-8,84; 15,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 10,63</t>
+          <t>-12,55; 11,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 17,58</t>
+          <t>-6,8; 17,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 38,58</t>
+          <t>-16,49; 38,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,27; 28,26</t>
+          <t>-25,47; 30,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,8; 48,22</t>
+          <t>-14,23; 46,44</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 19,71</t>
+          <t>-4,38; 19,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 20,41</t>
+          <t>-2,21; 19,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 13,76</t>
+          <t>-11,78; 13,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 46,26</t>
+          <t>-7,74; 45,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 54,83</t>
+          <t>-4,13; 52,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,03; 27,39</t>
+          <t>-18,81; 25,81</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 11,48</t>
+          <t>-11,48; 11,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 17,38</t>
+          <t>-9,87; 18,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,9; 13,75</t>
+          <t>-17,44; 13,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 18,91</t>
+          <t>-16,2; 19,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 41,3</t>
+          <t>-16,24; 41,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,67; 24,55</t>
+          <t>-23,96; 24,47</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 14,67</t>
+          <t>-1,16; 14,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 1,4</t>
+          <t>-13,63; 1,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 18,06</t>
+          <t>-7,13; 18,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 25,06</t>
+          <t>-1,69; 24,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 3,52</t>
+          <t>-22,43; 4,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 31,87</t>
+          <t>-11,08; 33,53</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 9,47</t>
+          <t>-9,43; 8,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 11,94</t>
+          <t>-6,87; 12,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 19,61</t>
+          <t>-5,53; 21,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 15,23</t>
+          <t>-12,93; 13,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 21,28</t>
+          <t>-10,48; 21,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 37,43</t>
+          <t>-7,59; 40,38</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 13,07</t>
+          <t>-13,66; 12,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,79; 8,55</t>
+          <t>-20,11; 8,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,19; 13,81</t>
+          <t>-14,84; 14,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 19,28</t>
+          <t>-17,2; 18,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,59; 17,77</t>
+          <t>-32,12; 18,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,48; 22,48</t>
+          <t>-19,81; 23,8</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 8,1</t>
+          <t>-0,69; 7,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 4,24</t>
+          <t>-4,25; 4,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 9,32</t>
+          <t>-2,23; 9,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 13,68</t>
+          <t>-1,1; 12,8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 8,25</t>
+          <t>-7,73; 8,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 16,44</t>
+          <t>-3,62; 16,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP04D$aparatos-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP04D$aparatos-Clase-trans_bre.xlsx
@@ -518,8 +518,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -604,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -619,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -632,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 15,66</t>
+          <t>-9,21; 13,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 11,11</t>
+          <t>-12,4; 11,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 17,26</t>
+          <t>-11,4; 12,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 38,32</t>
+          <t>-18,12; 34,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 30,41</t>
+          <t>-26,43; 29,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 46,44</t>
+          <t>-21,73; 31,14</t>
         </is>
       </c>
     </row>
@@ -684,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -699,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -712,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 19,3</t>
+          <t>-3,8; 21,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 19,47</t>
+          <t>-2,12; 19,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 13,01</t>
+          <t>-12,17; 12,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 45,92</t>
+          <t>-6,64; 51,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 52,23</t>
+          <t>-4,18; 52,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,81; 25,81</t>
+          <t>-19,0; 25,56</t>
         </is>
       </c>
     </row>
@@ -764,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,31</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -779,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,53%</t>
+          <t>-4,38%</t>
         </is>
       </c>
     </row>
@@ -792,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 11,89</t>
+          <t>-11,47; 11,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 18,02</t>
+          <t>-8,7; 19,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,44; 13,79</t>
+          <t>-18,87; 10,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 19,41</t>
+          <t>-15,97; 20,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 41,7</t>
+          <t>-15,55; 45,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,96; 24,47</t>
+          <t>-25,02; 18,09</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,0</t>
+          <t>2,75</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -859,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -872,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 14,18</t>
+          <t>-0,16; 14,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 1,89</t>
+          <t>-13,69; 1,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 18,64</t>
+          <t>-6,14; 12,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 24,09</t>
+          <t>-0,16; 25,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 4,01</t>
+          <t>-22,49; 3,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 33,53</t>
+          <t>-9,47; 21,72</t>
         </is>
       </c>
     </row>
@@ -924,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -939,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -952,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 8,43</t>
+          <t>-10,02; 8,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 12,44</t>
+          <t>-6,98; 12,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 21,0</t>
+          <t>-6,51; 17,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 13,3</t>
+          <t>-14,06; 13,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 21,57</t>
+          <t>-10,51; 21,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 40,38</t>
+          <t>-8,87; 31,4</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,17</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1019,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-0,39%</t>
+          <t>-0,24%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 12,65</t>
+          <t>-11,84; 14,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 8,92</t>
+          <t>-20,38; 9,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 14,25</t>
+          <t>-14,34; 13,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 18,27</t>
+          <t>-14,85; 21,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,12; 18,76</t>
+          <t>-33,19; 19,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,81; 23,8</t>
+          <t>-18,69; 21,51</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,22</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,56</t>
+          <t>-0,76; 7,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,43</t>
+          <t>-4,37; 4,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 9,35</t>
+          <t>-3,42; 6,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 12,8</t>
+          <t>-1,19; 12,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 8,76</t>
+          <t>-8,0; 9,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 16,38</t>
+          <t>-5,4; 11,75</t>
         </is>
       </c>
     </row>
